--- a/education_forms/030_online_learning_survey--education_forms.xlsx
+++ b/education_forms/030_online_learning_survey--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -853,8 +853,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -882,12 +882,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'option_1',_'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'option_1', 'value': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'option_2',_'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'option_2', 'value': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'option_3',_'value':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'option_3', 'value': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'option_4',_'value':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'option_4', 'value': 'Option 4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'option_5',_'value':_'option_5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'option_5', 'value': 'Option 5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'option_6',_'value':_'option_6'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'option_6', 'value': 'Option 6'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'option_7',_'value':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'option_7', 'value': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'option_8',_'value':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'option_8', 'value': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'option_9',_'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'option_9', 'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'option_10',_'value':_'likely'}</t>
+          <t>likely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'option_10', 'value': 'Likely'}</t>
+          <t>Likely</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'option_11',_'value':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'option_11', 'value': 'Not Likely'}</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'option_12',_'value':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'option_12', 'value': 'Very Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
